--- a/data/flight/titer/Ecoli_BC_LSMMG_1B.xlsx
+++ b/data/flight/titer/Ecoli_BC_LSMMG_1B.xlsx
@@ -1,59 +1,153 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipjos\code\DARPA\data\flight\titer\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ipjos\code\DARPA_FINAL\data\flight_uploaded_to_github_with_96_hours\growth\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7792A202-0C12-4E35-995C-C72E32E294AD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58F07CD1-93FA-4ADF-99BA-AA7480EF8018}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9015" yWindow="1770" windowWidth="24915" windowHeight="12525" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1950" yWindow="1950" windowWidth="26385" windowHeight="14250" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="growth" sheetId="1" r:id="rId1"/>
     <sheet name="titer" sheetId="2" r:id="rId2"/>
+    <sheet name="README" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
+    </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="46" uniqueCount="19">
   <si>
     <t>BR1</t>
   </si>
   <si>
+    <t>BR2</t>
+  </si>
+  <si>
+    <t>TR1</t>
+  </si>
+  <si>
+    <t>TR2</t>
+  </si>
+  <si>
+    <t>TR3</t>
+  </si>
+  <si>
+    <t>Microorganism name</t>
+  </si>
+  <si>
+    <t>Biomanufacturing performance</t>
+  </si>
+  <si>
+    <t>producer strain</t>
+  </si>
+  <si>
+    <t>Plasmid levels</t>
+  </si>
+  <si>
+    <t>Plasmid levels columns</t>
+  </si>
+  <si>
+    <t>Titer</t>
+  </si>
+  <si>
+    <t>producing strain</t>
+  </si>
+  <si>
+    <t>Culture volune</t>
+  </si>
+  <si>
+    <t>3ml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Low copy number </t>
+  </si>
+  <si>
+    <t>Antibiotic in media?</t>
+  </si>
+  <si>
+    <t>yes</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">E. coli MG1655 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>(motile)</t>
+    </r>
+  </si>
+  <si>
     <t>Hours</t>
-  </si>
-  <si>
-    <t>TR1</t>
-  </si>
-  <si>
-    <t>TR2</t>
-  </si>
-  <si>
-    <t>TR3</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Arial"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -76,8 +170,17 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -358,10 +461,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D6"/>
+  <dimension ref="A1:AK15"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="6" width="13.5703125" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="B1" t="s">
         <v>0</v>
       </c>
@@ -371,166 +477,432 @@
       <c r="D1" t="s">
         <v>0</v>
       </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E1" t="s">
+        <v>1</v>
+      </c>
+      <c r="F1" t="s">
+        <v>1</v>
+      </c>
+      <c r="G1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="C2" t="s">
+      <c r="C2" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A3">
-        <v>60</v>
-      </c>
-      <c r="B3">
-        <v>0.29899999999999999</v>
-      </c>
-      <c r="C3">
-        <v>0.31</v>
-      </c>
-      <c r="D3">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>60</v>
-      </c>
-      <c r="B4">
+        <v>96</v>
+      </c>
+      <c r="B3" s="3">
+        <v>0.23200000000000001</v>
+      </c>
+      <c r="C3" s="3">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="D3" s="3">
+        <v>0.20300000000000001</v>
+      </c>
+      <c r="E3" s="3">
+        <v>0.27800000000000002</v>
+      </c>
+      <c r="F3" s="3">
+        <v>0.28199999999999997</v>
+      </c>
+      <c r="G3" s="3">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="H3" s="3">
+        <v>0.27400000000000002</v>
+      </c>
+      <c r="I3" s="3">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="K3" s="3">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="L3" s="3">
+        <v>0.26900000000000002</v>
+      </c>
+      <c r="M3" s="3">
+        <v>0.26</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3">
+        <v>0.27100000000000002</v>
+      </c>
+      <c r="AB3" s="3">
+        <v>0.23699999999999999</v>
+      </c>
+      <c r="AC3" s="3">
         <v>0.24299999999999999</v>
       </c>
-      <c r="C4">
-        <v>0.32500000000000001</v>
-      </c>
-      <c r="D4">
-        <v>0.31</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>60</v>
-      </c>
-      <c r="B5">
-        <v>0.28899999999999998</v>
-      </c>
-      <c r="C5">
-        <v>0.29799999999999999</v>
-      </c>
-      <c r="D5">
-        <v>0.3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>60</v>
-      </c>
-      <c r="B6">
-        <v>0.33500000000000002</v>
-      </c>
-      <c r="C6">
-        <v>0.34200000000000003</v>
-      </c>
-      <c r="D6">
-        <v>0.33200000000000002</v>
-      </c>
+      <c r="AD3" s="3">
+        <v>0.26500000000000001</v>
+      </c>
+      <c r="AE3" s="3">
+        <v>0.25900000000000001</v>
+      </c>
+      <c r="AF3" s="3">
+        <v>0.27600000000000002</v>
+      </c>
+      <c r="AG3" s="3">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="AH3" s="3">
+        <v>0.30199999999999999</v>
+      </c>
+      <c r="AI3" s="3">
+        <v>0.24099999999999999</v>
+      </c>
+      <c r="AJ3" s="3">
+        <v>0.24399999999999999</v>
+      </c>
+      <c r="AK3" s="3">
+        <v>0.24199999999999999</v>
+      </c>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+      <c r="C4" s="3"/>
+      <c r="D4" s="3"/>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="B5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+      <c r="E10" s="1"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+      <c r="C11" s="1"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="1"/>
+    </row>
+    <row r="14" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="E14" s="1"/>
+    </row>
+    <row r="15" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="E15" s="1"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="1" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{67820D14-AE55-4601-AB4D-CB8AD178327A}">
+  <dimension ref="A1:AK13"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="5" width="15.28515625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A3">
+        <v>96</v>
+      </c>
+      <c r="B3" s="3">
+        <v>1.2324929971988794</v>
+      </c>
+      <c r="C3" s="3">
+        <v>1.1120448179271707</v>
+      </c>
+      <c r="D3" s="3">
+        <v>1.0784313725490196</v>
+      </c>
+      <c r="E3" s="3">
+        <v>1.1624649859943976</v>
+      </c>
+      <c r="F3" s="3">
+        <v>1.3641456582633054</v>
+      </c>
+      <c r="G3" s="3">
+        <v>1.187675070028011</v>
+      </c>
+      <c r="H3" s="3">
+        <v>1.0840336134453781</v>
+      </c>
+      <c r="I3" s="3">
+        <v>1.002801120448179</v>
+      </c>
+      <c r="J3" s="3">
+        <v>0.94397759103641443</v>
+      </c>
+      <c r="K3" s="3">
+        <v>1.1932773109243695</v>
+      </c>
+      <c r="L3" s="3">
+        <v>1.1764705882352939</v>
+      </c>
+      <c r="M3" s="3">
+        <v>1.2464985994397759</v>
+      </c>
+      <c r="N3" s="3"/>
+      <c r="O3" s="3"/>
+      <c r="P3" s="3"/>
+      <c r="Q3" s="3"/>
+      <c r="R3" s="3"/>
+      <c r="S3" s="3"/>
+      <c r="T3" s="3"/>
+      <c r="U3" s="3"/>
+      <c r="V3" s="3"/>
+      <c r="W3" s="3"/>
+      <c r="X3" s="3"/>
+      <c r="Y3" s="3"/>
+      <c r="Z3" s="3"/>
+      <c r="AA3" s="3"/>
+      <c r="AB3" s="3"/>
+      <c r="AC3" s="3"/>
+      <c r="AD3" s="3"/>
+      <c r="AE3" s="3"/>
+      <c r="AF3" s="3"/>
+      <c r="AG3" s="3"/>
+      <c r="AH3" s="3"/>
+      <c r="AI3" s="3"/>
+      <c r="AJ3" s="3"/>
+      <c r="AK3" s="3"/>
+    </row>
+    <row r="4" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A4" s="2"/>
+    </row>
+    <row r="5" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A5" s="2"/>
+      <c r="C5" s="3"/>
+      <c r="D5" s="3"/>
+      <c r="E5" s="3"/>
+    </row>
+    <row r="6" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A6" s="2"/>
+      <c r="C6" s="3"/>
+      <c r="D6" s="3"/>
+      <c r="E6" s="3"/>
+    </row>
+    <row r="7" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A7" s="2"/>
+      <c r="C7" s="3"/>
+      <c r="D7" s="3"/>
+      <c r="E7" s="3"/>
+    </row>
+    <row r="8" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A8" s="2"/>
+      <c r="C8" s="3"/>
+      <c r="D8" s="3"/>
+      <c r="E8" s="3"/>
+    </row>
+    <row r="9" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A9" s="2"/>
+      <c r="C9" s="3"/>
+      <c r="D9" s="3"/>
+      <c r="E9" s="3"/>
+    </row>
+    <row r="10" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A10" s="2"/>
+    </row>
+    <row r="11" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A11" s="2"/>
+    </row>
+    <row r="12" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A12" s="2"/>
+    </row>
+    <row r="13" spans="1:37" x14ac:dyDescent="0.25">
+      <c r="A13" s="2"/>
+      <c r="E13" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FEB7C6C5-672C-48B6-9238-68A34D5276B7}">
-  <dimension ref="A1:D6"/>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9C5B29F-B2ED-4FDE-BD7E-A42BB3247F1C}">
+  <dimension ref="A1:B7"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="4" width="44.7109375" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>5</v>
+      </c>
       <c r="B1" t="s">
-        <v>0</v>
-      </c>
-      <c r="C1" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="B2" t="s">
-        <v>2</v>
-      </c>
-      <c r="C2" t="s">
-        <v>3</v>
-      </c>
-      <c r="D2" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A3">
-        <v>60</v>
-      </c>
-      <c r="B3">
-        <v>1.6579999999999999</v>
-      </c>
-      <c r="C3">
-        <v>1.585</v>
-      </c>
-      <c r="D3">
-        <v>1.5960000000000001</v>
-      </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A4">
-        <v>60</v>
-      </c>
-      <c r="B4">
-        <v>1.5820000000000001</v>
-      </c>
-      <c r="C4">
-        <v>1.4733000000000001</v>
-      </c>
-      <c r="D4">
-        <v>1.431</v>
-      </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A5">
-        <v>60</v>
-      </c>
-      <c r="B5">
-        <v>1.6859999999999999</v>
-      </c>
-      <c r="C5">
-        <v>1.7729999999999999</v>
-      </c>
-      <c r="D5">
-        <v>1.694</v>
-      </c>
-    </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A6">
-        <v>60</v>
-      </c>
-      <c r="B6">
-        <v>1.9239999999999999</v>
-      </c>
-      <c r="C6">
-        <v>2.028</v>
-      </c>
-      <c r="D6">
-        <v>2.2010000000000001</v>
+        <v>7</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>10</v>
+      </c>
+      <c r="B6" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" ht="20.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" t="s">
+        <v>13</v>
       </c>
     </row>
   </sheetData>
